--- a/Outputs/Scenarios/PtX_demand_EE_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_EE_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0003495342219082036</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00126691832694766</v>
+        <v>0.001373432080341904</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0002849629009483629</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00253383665389532</v>
+        <v>0.002279703207586904</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>5.036196475490044e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0004223061089825534</v>
+        <v>0.0002849629009483629</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0005174428610021083</v>
       </c>
       <c r="K30" t="n">
-        <v>0.006838011754025995</v>
+        <v>0.007412904611902663</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.001538046790151732</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01367602350805199</v>
+        <v>0.01230437432121386</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>2.723383478958465e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002279337251341998</v>
+        <v>0.001538046790151732</v>
       </c>
     </row>
     <row r="43">
